--- a/Tubex_July26.xlsx
+++ b/Tubex_July26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D1DF46270FC10E5B39B1DE3FF96FE2226285E9D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_18C07461DDC8092399517A07B5E8AE649427E1A4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3603,6 +3603,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -3615,13 +3622,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -3663,20 +3663,20 @@
     </border>
   </borders>
   <cellStyleXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29"/>
-    <xf numFmtId="172" fontId="24" fillId="0" borderId="29"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28"/>
+    <xf numFmtId="172" fontId="24" fillId="0" borderId="28"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="29"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28"/>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="28"/>
   </cellStyleXfs>
   <cellXfs count="285">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -4301,10 +4301,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4366,48 +4366,48 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="36" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="36" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -4419,25 +4419,25 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4884,8 +4884,8 @@
     <col min="13" max="13" width="14.7109375" style="131" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="131" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="131" customWidth="1"/>
-    <col min="16" max="112" width="8.7109375" style="131" customWidth="1"/>
-    <col min="113" max="16384" width="8.7109375" style="131"/>
+    <col min="16" max="113" width="8.7109375" style="131" customWidth="1"/>
+    <col min="114" max="16384" width="8.7109375" style="131"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -65694,14 +65694,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -69507,7 +69507,6 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A156:F156"/>
@@ -69516,6 +69515,7 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A22:F22"/>

--- a/Tubex_July26.xlsx
+++ b/Tubex_July26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_18C07461DDC8092399517A07B5E8AE649427E1A4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2466752B3DD4BD039605922945BC21140F12CB08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4816" uniqueCount="916">
   <si>
     <t>TUBEX  — July 2026 Month to Date Report</t>
   </si>
@@ -1847,7 +1847,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 24-Jul-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 25-Jul-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -1871,7 +1871,7 @@
     <t>Cap Item ID (auto)</t>
   </si>
   <si>
-    <t>200ml</t>
+    <t>120ml</t>
   </si>
   <si>
     <t>OK</t>
@@ -1880,10 +1880,10 @@
     <t>Ready for dispatch</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>32</t>
-  </si>
-  <si>
-    <t>30</t>
   </si>
   <si>
     <t>35</t>
@@ -4884,8 +4884,8 @@
     <col min="13" max="13" width="14.7109375" style="131" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="131" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="131" customWidth="1"/>
-    <col min="16" max="113" width="8.7109375" style="131" customWidth="1"/>
-    <col min="114" max="16384" width="8.7109375" style="131"/>
+    <col min="16" max="114" width="8.7109375" style="131" customWidth="1"/>
+    <col min="115" max="16384" width="8.7109375" style="131"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5061,24 +5061,24 @@
       <c r="A6" s="128"/>
       <c r="B6" s="264">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>0</v>
+        <v>24990</v>
       </c>
       <c r="C6" s="261"/>
       <c r="D6" s="137">
         <f>SUMIF($B$11:$B$64,"TUBE",$H$11:$H$64)</f>
-        <v>236236</v>
+        <v>261226</v>
       </c>
       <c r="E6" s="264"/>
       <c r="F6" s="261"/>
       <c r="G6" s="138">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),"-")</f>
-        <v>2.613613877712552E-2</v>
+        <v>2.5334308399498538E-2</v>
       </c>
       <c r="H6" s="138"/>
       <c r="I6" s="135"/>
       <c r="J6" s="264">
         <f>SUMIF($B$11:$B$64,"TUBE",$K$11:$K$64)</f>
-        <v>290486</v>
+        <v>295190</v>
       </c>
       <c r="K6" s="261"/>
       <c r="L6" s="139"/>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="O7" s="151">
         <f t="shared" ref="O7:O13" si="0">IFERROR(N7/$N$14,"")</f>
-        <v>0.48684210526315791</v>
+        <v>0.47741935483870968</v>
       </c>
       <c r="P7" s="128"/>
       <c r="Q7" s="128"/>
@@ -5158,18 +5158,18 @@
       <c r="A8" s="128"/>
       <c r="B8" s="269">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$H$3:$H$8963)</f>
-        <v>9000</v>
+        <v>6360</v>
       </c>
       <c r="C8" s="261"/>
       <c r="D8" s="143">
         <f>SUMIF($B$11:$B$64,"PET",$H$11:$H$64)</f>
-        <v>61240</v>
+        <v>67600</v>
       </c>
       <c r="E8" s="269"/>
       <c r="F8" s="261"/>
       <c r="G8" s="144">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),0)</f>
-        <v>6.9159446724426199E-2</v>
+        <v>7.0790378006872851E-2</v>
       </c>
       <c r="H8" s="144"/>
       <c r="I8" s="142"/>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="O8" s="151">
         <f t="shared" si="0"/>
-        <v>0.17105263157894737</v>
+        <v>0.16774193548387098</v>
       </c>
       <c r="P8" s="128"/>
       <c r="Q8" s="128"/>
@@ -5223,15 +5223,15 @@
       <c r="L9" s="271"/>
       <c r="M9" s="149" t="str">
         <f>IFERROR(INDEX($S$9:$S$21,MATCH(LARGE($U$9:$U$21,3),$U$9:$U$21,0)),"")</f>
-        <v>Operations</v>
+        <v>Mechanical</v>
       </c>
       <c r="N9" s="150">
         <f>IFERROR(INDEX($T$9:$T$21,MATCH(LARGE($U$9:$U$21,3),$U$9:$U$21,0)),"")/60</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O9" s="151">
         <f t="shared" si="0"/>
-        <v>0.15131578947368421</v>
+        <v>0.15483870967741936</v>
       </c>
       <c r="P9" s="128"/>
       <c r="Q9" s="128"/>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="T9" s="160">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$8963,5)="Press")+(LEFT(Production_Log!$B$3:$B$8963,5)="Print"))*Production_Log!$K$3:$K$8963)</f>
-        <v>1260</v>
+        <v>1440</v>
       </c>
       <c r="U9" s="159">
         <f>T9+0.00001</f>
-        <v>1260.00001</v>
+        <v>1440.00001</v>
       </c>
       <c r="V9" s="130"/>
       <c r="W9" s="130"/>
@@ -5293,15 +5293,15 @@
       </c>
       <c r="M10" s="149" t="str">
         <f>IFERROR(INDEX($S$9:$S$21,MATCH(LARGE($U$9:$U$21,4),$U$9:$U$21,0)),"")</f>
-        <v>Mechanical</v>
+        <v>Operations</v>
       </c>
       <c r="N10" s="150">
         <f>IFERROR(INDEX($T$9:$T$21,MATCH(LARGE($U$9:$U$21,4),$U$9:$U$21,0)),"")/60</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O10" s="151">
         <f t="shared" si="0"/>
-        <v>0.13815789473684212</v>
+        <v>0.14838709677419354</v>
       </c>
       <c r="P10" s="128"/>
       <c r="Q10" s="128"/>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="O11" s="151">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>5.1612903225806452E-2</v>
       </c>
       <c r="P11" s="161"/>
       <c r="Q11" s="161"/>
@@ -5490,7 +5490,7 @@
         <v>-</v>
       </c>
       <c r="K13" s="252">
-        <v>95088</v>
+        <v>99792</v>
       </c>
       <c r="L13" s="254"/>
       <c r="M13" s="149" t="str">
@@ -5551,15 +5551,15 @@
       </c>
       <c r="H14" s="252">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F14)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>151074</v>
+        <v>176064</v>
       </c>
       <c r="I14" s="251">
         <f>G14-H14</f>
-        <v>340676</v>
+        <v>315686</v>
       </c>
       <c r="J14" s="253">
         <f>IF(G14=0,"-",H14/G14)</f>
-        <v>0.30721708185053381</v>
+        <v>0.35803558718861211</v>
       </c>
       <c r="K14" s="252">
         <v>195398</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="N14" s="147">
         <f>SUM($T$9:$T$21)/60</f>
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O14" s="147" t="s">
         <v>37</v>
@@ -5663,16 +5663,16 @@
       </c>
       <c r="H16" s="258">
         <f>SUM(H11:H15)</f>
-        <v>236236</v>
+        <v>261226</v>
       </c>
       <c r="I16" s="258">
         <f>SUMIF(I11:I15,"&gt;"&amp;0)</f>
-        <v>510930</v>
+        <v>485940</v>
       </c>
       <c r="J16" s="258"/>
       <c r="K16" s="258">
         <f>SUM(K11:K15)</f>
-        <v>290486</v>
+        <v>295190</v>
       </c>
       <c r="L16" s="258"/>
       <c r="M16" s="128"/>
@@ -5723,15 +5723,15 @@
       </c>
       <c r="H17" s="252">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F17)*Production_Log!$H$3:$H$8963)</f>
-        <v>0</v>
+        <v>6360</v>
       </c>
       <c r="I17" s="251">
         <f t="shared" ref="I17:I23" si="1">G17-H17</f>
-        <v>53240</v>
+        <v>46880</v>
       </c>
       <c r="J17" s="253">
         <f t="shared" ref="J17:J23" si="2">IF(G17=0,"-",H17/G17)</f>
-        <v>0</v>
+        <v>0.11945905334335086</v>
       </c>
       <c r="K17" s="252"/>
       <c r="L17" s="254"/>
@@ -5966,7 +5966,7 @@
       <c r="AB21" s="130"/>
       <c r="AC21" s="130"/>
     </row>
-    <row r="22" spans="1:29" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="128"/>
       <c r="B22" s="247" t="s">
         <v>42</v>
@@ -5984,7 +5984,7 @@
         <v>8006</v>
       </c>
       <c r="G22" s="251">
-        <v>42200</v>
+        <v>42240</v>
       </c>
       <c r="H22" s="252">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F22)*Production_Log!$H$3:$H$8963)</f>
@@ -5992,11 +5992,11 @@
       </c>
       <c r="I22" s="251">
         <f t="shared" si="1"/>
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="J22" s="253">
         <f t="shared" si="2"/>
-        <v>1.0009478672985781</v>
+        <v>1</v>
       </c>
       <c r="K22" s="252">
         <v>6840</v>
@@ -6085,15 +6085,15 @@
       <c r="F24" s="256"/>
       <c r="G24" s="258">
         <f>SUM(G17:G23)</f>
-        <v>372107</v>
+        <v>372147</v>
       </c>
       <c r="H24" s="258">
         <f>SUM(H17:H23)</f>
-        <v>61240</v>
+        <v>67600</v>
       </c>
       <c r="I24" s="258">
         <f>SUMIF(I17:I23,"&gt;"&amp;0)</f>
-        <v>310907</v>
+        <v>304547</v>
       </c>
       <c r="J24" s="258"/>
       <c r="K24" s="258">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="H1" s="155">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -10083,11 +10083,11 @@
       </c>
       <c r="G6" s="176">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D6,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>151074</v>
+        <v>176064</v>
       </c>
       <c r="H6" s="177">
         <f>F6-G6</f>
-        <v>340676</v>
+        <v>315686</v>
       </c>
       <c r="I6" s="177"/>
     </row>
@@ -10105,11 +10105,11 @@
       </c>
       <c r="G7" s="148">
         <f>SUM(G3:G6)</f>
-        <v>236236</v>
+        <v>261226</v>
       </c>
       <c r="H7" s="148">
         <f>SUMIF(H3:H6, "&gt;0")</f>
-        <v>510930</v>
+        <v>485940</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="11"/>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="F17" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A17,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A17,TableInventory[Item ID],0)),0)</f>
-        <v>603</v>
+        <v>569</v>
       </c>
       <c r="G17" s="31">
         <f t="shared" si="0"/>
-        <v>-212.24070979999999</v>
+        <v>-246.24070979999999</v>
       </c>
       <c r="H17" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A17)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A17)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A17)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A17)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A17)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A17)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A17)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A17)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A17)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A17)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A17)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A17)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -10579,15 +10579,15 @@
       </c>
       <c r="E20" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A20)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>3393.9488000000001</v>
+        <v>3174.0368000000003</v>
       </c>
       <c r="F20" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A20,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A20,TableInventory[Item ID],0)),0)</f>
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="G20" s="31">
         <f t="shared" si="0"/>
-        <v>-3146.9488000000001</v>
+        <v>-2860.0368000000003</v>
       </c>
       <c r="H20" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E28" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A28)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>162.99614936</v>
+        <v>155.29922936000003</v>
       </c>
       <c r="F28" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A28,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A28,TableInventory[Item ID],0)),0)</f>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="G28" s="31">
         <f t="shared" si="0"/>
-        <v>-87.996149360000004</v>
+        <v>-80.299229360000027</v>
       </c>
       <c r="H28" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A28)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A28)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A28)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A28)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A28)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A28)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A28)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A28)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A28)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A28)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A28)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A28)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E32" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A32)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>368.40693120000003</v>
+        <v>349.98930120000006</v>
       </c>
       <c r="F32" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A32,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A32,TableInventory[Item ID],0)),0)</f>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G32" s="31">
         <f t="shared" si="0"/>
-        <v>-128.40693120000003</v>
+        <v>-109.98930120000006</v>
       </c>
       <c r="H32" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="E40" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A40)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>110.86820800000001</v>
+        <v>103.17128800000002</v>
       </c>
       <c r="F40" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A40,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A40,TableInventory[Item ID],0)),0)</f>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G40" s="31">
         <f t="shared" si="0"/>
-        <v>-50.86820800000001</v>
+        <v>-43.171288000000018</v>
       </c>
       <c r="H40" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A40)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A40)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A40)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A40)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A40)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A40)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A40)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A40)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A40)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A40)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A40)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A40)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="E55" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A55)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>475248.60000000003</v>
+        <v>449758.8</v>
       </c>
       <c r="F55" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A55,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A55,TableInventory[Item ID],0)),0)</f>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="G55" s="31">
         <f t="shared" si="3"/>
-        <v>-405248.60000000003</v>
+        <v>-379758.8</v>
       </c>
       <c r="H55" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A55)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A55)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A55)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A55)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A55)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A55)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A55)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A55)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A55)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A55)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A55)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A55)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="E68" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A68)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>2192.55320416</v>
+        <v>2077.0554217600002</v>
       </c>
       <c r="F68" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A68,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A68,TableInventory[Item ID],0)),0)</f>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="G68" s="31">
         <f t="shared" si="3"/>
-        <v>-1992.55320416</v>
+        <v>-1877.0554217600002</v>
       </c>
       <c r="H68" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A68)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A68)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A68)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A68)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A68)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A68)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A68)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A68)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A68)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A68)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A68)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A68)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E72" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A72)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>3.9652100620000006</v>
+        <v>3.7365015819999998</v>
       </c>
       <c r="F72" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A72,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A72,TableInventory[Item ID],0)),0)</f>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="G72" s="31">
         <f t="shared" si="3"/>
-        <v>16.034789937999999</v>
+        <v>16.263498418000001</v>
       </c>
       <c r="H72" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A72)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A72)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A72)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A72)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A72)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A72)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A72)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A72)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A72)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A72)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A72)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A72)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="E74" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A74)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>257.9240686</v>
+        <v>253.63578460000002</v>
       </c>
       <c r="F74" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A74,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A74,TableInventory[Item ID],0)),0)</f>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="G74" s="31">
         <f t="shared" ref="G74:G105" si="6">F74-E74</f>
-        <v>231.0759314</v>
+        <v>235.36421539999998</v>
       </c>
       <c r="H74" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -13284,11 +13284,11 @@
       </c>
       <c r="G96" s="38">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D96,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>0</v>
+        <v>6360</v>
       </c>
       <c r="H96" s="39">
         <f t="shared" ref="H96:H101" si="7">F96-G96</f>
-        <v>53240</v>
+        <v>46880</v>
       </c>
       <c r="I96" s="29"/>
     </row>
@@ -13369,7 +13369,7 @@
         <v>335</v>
       </c>
       <c r="F99" s="37">
-        <v>73840</v>
+        <v>42240</v>
       </c>
       <c r="G99" s="180">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D99,Tubex_Dashboard!$F$11:$F$100,0))</f>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="H99" s="186">
         <f t="shared" si="7"/>
-        <v>31600</v>
+        <v>0</v>
       </c>
       <c r="I99" s="181"/>
     </row>
@@ -13451,15 +13451,15 @@
       </c>
       <c r="F102" s="148">
         <f>SUM(F96:F101)</f>
-        <v>403747</v>
+        <v>372147</v>
       </c>
       <c r="G102" s="148">
         <f>SUM(G96:G101)</f>
-        <v>61240</v>
+        <v>67600</v>
       </c>
       <c r="H102" s="148">
         <f>SUM(H96:H101)</f>
-        <v>342507</v>
+        <v>304547</v>
       </c>
       <c r="I102" s="12"/>
       <c r="J102" s="11"/>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="E105" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A105)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>8346.502199999999</v>
+        <v>7358.3577999999998</v>
       </c>
       <c r="F105" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A105,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A105,TableInventory[Item ID],0)),0)</f>
@@ -13537,11 +13537,11 @@
       </c>
       <c r="G105" s="22">
         <f t="shared" ref="G105:G111" si="8">F105-E105</f>
-        <v>-5346.502199999999</v>
+        <v>-4358.3577999999998</v>
       </c>
       <c r="H105" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A105)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A105)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A105)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
-        <v>PET BOTTLE SMALL (120ML) YELLOW, PET BOTTLE COCONUT OIL (200ML) WHITE, PET BOTTLE LARGE (200 ML) YELLOW, PET BOTTLE 130ML WHITE, PET BOTTLE (150ML)TRANSPARENT BODY MIST</v>
+        <v>PET BOTTLE SMALL (120ML) YELLOW, PET BOTTLE COCONUT OIL (200ML) WHITE, PET BOTTLE 130ML WHITE, PET BOTTLE (150ML)TRANSPARENT BODY MIST</v>
       </c>
       <c r="I105" s="46" t="str">
         <f t="shared" ref="I105:I111" si="9">IF(E105=0,"Not needed",IF(G105&lt;0,"SHORTAGE",IF(G105&lt;F105*0.1,"LOW","OK")))</f>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="E106" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A106)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>100.52839999999999</v>
+        <v>48.520799999999994</v>
       </c>
       <c r="F106" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A106,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A106,TableInventory[Item ID],0)),0)</f>
@@ -13571,11 +13571,11 @@
       </c>
       <c r="G106" s="22">
         <f t="shared" si="8"/>
-        <v>-100.52839999999999</v>
+        <v>-48.520799999999994</v>
       </c>
       <c r="H106" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A106)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A106)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A106)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A106)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A106)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A106)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A106)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A106)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A106)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A106)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A106)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A106)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A106)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A106)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A106)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A106)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A106)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A106)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
-        <v>PET BOTTLE SMALL (120ML) YELLOW, PET BOTTLE LARGE (200 ML) YELLOW</v>
+        <v>PET BOTTLE SMALL (120ML) YELLOW</v>
       </c>
       <c r="I106" s="46" t="str">
         <f t="shared" si="9"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="E109" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A109)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>3099.4629247999997</v>
+        <v>3038.5153627999998</v>
       </c>
       <c r="F109" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A109,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A109,TableInventory[Item ID],0)),0)</f>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="G109" s="22">
         <f t="shared" si="8"/>
-        <v>-3024.4629247999997</v>
+        <v>-2963.5153627999998</v>
       </c>
       <c r="H109" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A109)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A109)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A109)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="E110" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A110)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>312.40417000000002</v>
+        <v>9.5829500000000003</v>
       </c>
       <c r="F110" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A110,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A110,TableInventory[Item ID],0)),0)</f>
@@ -13707,15 +13707,15 @@
       </c>
       <c r="G110" s="22">
         <f t="shared" si="8"/>
-        <v>-162.40417000000002</v>
+        <v>140.41704999999999</v>
       </c>
       <c r="H110" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A110)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A110)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A110)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A110)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A110)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A110)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A110)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A110)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A110)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A110)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A110)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A110)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A110)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A110)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A110)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A110)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A110)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A110)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
-        <v>PET BOTTLE COCONUT OIL (200ML) WHITE, PET BOTTLE LARGE (200 ML) YELLOW</v>
+        <v>PET BOTTLE COCONUT OIL (200ML) WHITE</v>
       </c>
       <c r="I110" s="47" t="str">
         <f t="shared" si="9"/>
-        <v>SHORTAGE</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="E111" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A111)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>1.96941525</v>
+        <v>1.75114525</v>
       </c>
       <c r="F111" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A111,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A111,TableInventory[Item ID],0)),0)</f>
@@ -13741,11 +13741,11 @@
       </c>
       <c r="G111" s="22">
         <f t="shared" si="8"/>
-        <v>-1.96941525</v>
+        <v>-1.75114525</v>
       </c>
       <c r="H111" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A111)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A111)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A111)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
-        <v>PET BOTTLE SMALL (120ML) YELLOW, PET BOTTLE COCONUT OIL (200ML) WHITE, PET BOTTLE LARGE (200 ML) YELLOW, PET BOTTLE 130ML WHITE, PET BOTTLE (150ML)TRANSPARENT BODY MIST</v>
+        <v>PET BOTTLE SMALL (120ML) YELLOW, PET BOTTLE COCONUT OIL (200ML) WHITE, PET BOTTLE 130ML WHITE, PET BOTTLE (150ML)TRANSPARENT BODY MIST</v>
       </c>
       <c r="I111" s="47" t="str">
         <f t="shared" si="9"/>
@@ -20252,109 +20252,222 @@
       <c r="S114" s="231"/>
     </row>
     <row r="115" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="194"/>
-      <c r="B115" s="195"/>
-      <c r="C115" s="195"/>
-      <c r="D115" s="195"/>
-      <c r="E115" s="195"/>
-      <c r="F115" s="195"/>
-      <c r="G115" s="196"/>
-      <c r="H115" s="196"/>
-      <c r="I115" s="196"/>
-      <c r="J115" s="197"/>
-      <c r="K115" s="195"/>
-      <c r="L115" s="195"/>
-      <c r="M115" s="195"/>
-      <c r="N115" s="195"/>
-      <c r="O115" s="195"/>
-      <c r="P115" s="195"/>
-      <c r="Q115" s="195"/>
-      <c r="R115" s="195"/>
-      <c r="S115" s="195"/>
+      <c r="A115" s="230">
+        <v>46227</v>
+      </c>
+      <c r="B115" s="231" t="s">
+        <v>294</v>
+      </c>
+      <c r="C115" s="231" t="s">
+        <v>34</v>
+      </c>
+      <c r="D115" s="231" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="231">
+        <v>30</v>
+      </c>
+      <c r="F115" s="231">
+        <v>6206</v>
+      </c>
+      <c r="G115" s="232">
+        <v>13000</v>
+      </c>
+      <c r="H115" s="232">
+        <v>12720</v>
+      </c>
+      <c r="I115" s="232">
+        <v>280</v>
+      </c>
+      <c r="J115" s="233">
+        <f t="shared" si="3"/>
+        <v>2.1538461538461538E-2</v>
+      </c>
+      <c r="K115" s="231"/>
+      <c r="L115" s="231"/>
+      <c r="M115" s="231">
+        <v>60</v>
+      </c>
+      <c r="N115" s="231"/>
+      <c r="O115" s="231"/>
+      <c r="P115" s="231"/>
+      <c r="Q115" s="231"/>
+      <c r="R115" s="231"/>
+      <c r="S115" s="231"/>
     </row>
     <row r="116" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="194"/>
-      <c r="B116" s="195"/>
-      <c r="C116" s="195"/>
-      <c r="D116" s="195"/>
-      <c r="E116" s="195"/>
-      <c r="F116" s="195"/>
-      <c r="G116" s="196"/>
-      <c r="H116" s="196"/>
-      <c r="I116" s="196"/>
-      <c r="J116" s="197"/>
-      <c r="K116" s="195"/>
-      <c r="L116" s="195"/>
-      <c r="M116" s="195"/>
-      <c r="N116" s="195"/>
-      <c r="O116" s="195"/>
-      <c r="P116" s="195"/>
-      <c r="Q116" s="195"/>
-      <c r="R116" s="195"/>
-      <c r="S116" s="195"/>
+      <c r="A116" s="230">
+        <v>46227</v>
+      </c>
+      <c r="B116" s="231" t="s">
+        <v>295</v>
+      </c>
+      <c r="C116" s="231" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="231" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="231">
+        <v>30</v>
+      </c>
+      <c r="F116" s="231">
+        <v>6206</v>
+      </c>
+      <c r="G116" s="232">
+        <v>26180</v>
+      </c>
+      <c r="H116" s="232">
+        <v>26160</v>
+      </c>
+      <c r="I116" s="232">
+        <v>20</v>
+      </c>
+      <c r="J116" s="233">
+        <f t="shared" si="3"/>
+        <v>7.6394194041252863E-4</v>
+      </c>
+      <c r="K116" s="231"/>
+      <c r="L116" s="231"/>
+      <c r="M116" s="231"/>
+      <c r="N116" s="231"/>
+      <c r="O116" s="231"/>
+      <c r="P116" s="231"/>
+      <c r="Q116" s="231"/>
+      <c r="R116" s="231"/>
+      <c r="S116" s="231"/>
     </row>
     <row r="117" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="194"/>
-      <c r="B117" s="195"/>
-      <c r="C117" s="195"/>
-      <c r="D117" s="195"/>
-      <c r="E117" s="195"/>
-      <c r="F117" s="195"/>
-      <c r="G117" s="196"/>
-      <c r="H117" s="196"/>
-      <c r="I117" s="196"/>
-      <c r="J117" s="197"/>
-      <c r="K117" s="195"/>
-      <c r="L117" s="195"/>
-      <c r="M117" s="195"/>
-      <c r="N117" s="195"/>
-      <c r="O117" s="195"/>
-      <c r="P117" s="195"/>
-      <c r="Q117" s="195"/>
-      <c r="R117" s="195"/>
-      <c r="S117" s="195"/>
+      <c r="A117" s="230">
+        <v>46227</v>
+      </c>
+      <c r="B117" s="231" t="s">
+        <v>296</v>
+      </c>
+      <c r="C117" s="231" t="s">
+        <v>28</v>
+      </c>
+      <c r="D117" s="231" t="s">
+        <v>43</v>
+      </c>
+      <c r="E117" s="231" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" s="231">
+        <v>8005</v>
+      </c>
+      <c r="G117" s="232">
+        <v>6960</v>
+      </c>
+      <c r="H117" s="232">
+        <v>6360</v>
+      </c>
+      <c r="I117" s="232">
+        <v>600</v>
+      </c>
+      <c r="J117" s="233">
+        <f t="shared" si="3"/>
+        <v>8.6206896551724144E-2</v>
+      </c>
+      <c r="K117" s="231">
+        <v>90</v>
+      </c>
+      <c r="L117" s="231"/>
+      <c r="M117" s="231"/>
+      <c r="N117" s="231">
+        <v>480</v>
+      </c>
+      <c r="O117" s="231"/>
+      <c r="P117" s="231"/>
+      <c r="Q117" s="231"/>
+      <c r="R117" s="231"/>
+      <c r="S117" s="231"/>
     </row>
     <row r="118" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="194"/>
-      <c r="B118" s="195"/>
-      <c r="C118" s="195"/>
-      <c r="D118" s="195"/>
-      <c r="E118" s="195"/>
-      <c r="F118" s="195"/>
-      <c r="G118" s="196"/>
-      <c r="H118" s="196"/>
-      <c r="I118" s="196"/>
-      <c r="J118" s="197"/>
-      <c r="K118" s="195"/>
-      <c r="L118" s="195"/>
-      <c r="M118" s="195"/>
-      <c r="N118" s="195"/>
-      <c r="O118" s="195"/>
-      <c r="P118" s="195"/>
-      <c r="Q118" s="195"/>
-      <c r="R118" s="195"/>
-      <c r="S118" s="195"/>
+      <c r="A118" s="230">
+        <v>46227</v>
+      </c>
+      <c r="B118" s="231" t="s">
+        <v>297</v>
+      </c>
+      <c r="C118" s="231" t="s">
+        <v>34</v>
+      </c>
+      <c r="D118" s="231" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="231">
+        <v>30</v>
+      </c>
+      <c r="F118" s="231">
+        <v>6206</v>
+      </c>
+      <c r="G118" s="232">
+        <v>12000</v>
+      </c>
+      <c r="H118" s="232">
+        <v>11890</v>
+      </c>
+      <c r="I118" s="232">
+        <v>110</v>
+      </c>
+      <c r="J118" s="233">
+        <f t="shared" si="3"/>
+        <v>9.1666666666666667E-3</v>
+      </c>
+      <c r="K118" s="231">
+        <v>180</v>
+      </c>
+      <c r="L118" s="231"/>
+      <c r="M118" s="231"/>
+      <c r="N118" s="231"/>
+      <c r="O118" s="231"/>
+      <c r="P118" s="231"/>
+      <c r="Q118" s="231"/>
+      <c r="R118" s="231"/>
+      <c r="S118" s="231"/>
     </row>
     <row r="119" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="194"/>
-      <c r="B119" s="195"/>
-      <c r="C119" s="195"/>
-      <c r="D119" s="195"/>
-      <c r="E119" s="195"/>
-      <c r="F119" s="195"/>
-      <c r="G119" s="196"/>
-      <c r="H119" s="196"/>
-      <c r="I119" s="196"/>
-      <c r="J119" s="197"/>
-      <c r="K119" s="195"/>
-      <c r="L119" s="195"/>
-      <c r="M119" s="195"/>
-      <c r="N119" s="195"/>
-      <c r="O119" s="195"/>
-      <c r="P119" s="195"/>
-      <c r="Q119" s="195"/>
-      <c r="R119" s="195"/>
-      <c r="S119" s="195"/>
+      <c r="A119" s="230">
+        <v>46227</v>
+      </c>
+      <c r="B119" s="231" t="s">
+        <v>299</v>
+      </c>
+      <c r="C119" s="231" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" s="231" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="231">
+        <v>30</v>
+      </c>
+      <c r="F119" s="231">
+        <v>6206</v>
+      </c>
+      <c r="G119" s="232">
+        <v>25440</v>
+      </c>
+      <c r="H119" s="232">
+        <v>24990</v>
+      </c>
+      <c r="I119" s="232">
+        <v>450</v>
+      </c>
+      <c r="J119" s="233">
+        <f t="shared" si="3"/>
+        <v>1.7688679245283018E-2</v>
+      </c>
+      <c r="K119" s="231"/>
+      <c r="L119" s="231"/>
+      <c r="M119" s="231"/>
+      <c r="N119" s="231"/>
+      <c r="O119" s="231"/>
+      <c r="P119" s="231"/>
+      <c r="Q119" s="231"/>
+      <c r="R119" s="231"/>
+      <c r="S119" s="231"/>
     </row>
     <row r="120" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="194"/>
@@ -55184,7 +55297,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" style="66" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="66" customWidth="1"/>
@@ -55211,7 +55324,7 @@
       </c>
       <c r="J1" s="69">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="70" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55403,11 +55516,11 @@
         <v>498</v>
       </c>
       <c r="I7" s="37">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="J7" s="203">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>101796</v>
+        <v>96056</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55437,11 +55550,11 @@
         <v>182</v>
       </c>
       <c r="I8" s="37">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="J8" s="203">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>30875</v>
+        <v>39250</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55525,7 +55638,7 @@
       <c r="I12" s="73"/>
       <c r="J12" s="69">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -65781,19 +65894,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="234">
-        <v>8007</v>
+        <v>8005</v>
       </c>
       <c r="C4" s="235" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="235" t="s">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="E4" s="234" t="s">
         <v>607</v>
       </c>
       <c r="F4" s="236">
-        <v>9000</v>
+        <v>6360</v>
       </c>
       <c r="G4" s="234" t="s">
         <v>608</v>
@@ -65811,19 +65924,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="234">
-        <v>6515</v>
+        <v>6206</v>
       </c>
       <c r="C5" s="235" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" s="235" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="E5" s="234" t="s">
         <v>610</v>
       </c>
       <c r="F5" s="236">
-        <v>36192</v>
+        <v>19000</v>
       </c>
       <c r="G5" s="234" t="s">
         <v>608</v>
@@ -65833,7 +65946,7 @@
       </c>
       <c r="I5" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B5)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>1073</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65841,19 +65954,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="234">
-        <v>4050</v>
+        <v>6515</v>
       </c>
       <c r="C6" s="235" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D6" s="235" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E6" s="234" t="s">
         <v>611</v>
       </c>
       <c r="F6" s="236">
-        <v>9450</v>
+        <v>36192</v>
       </c>
       <c r="G6" s="234" t="s">
         <v>608</v>
@@ -65863,7 +65976,7 @@
       </c>
       <c r="I6" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B6)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65871,19 +65984,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="234">
-        <v>6337</v>
+        <v>4050</v>
       </c>
       <c r="C7" s="235" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D7" s="235" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E7" s="234" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F7" s="236">
-        <v>15680</v>
+        <v>9450</v>
       </c>
       <c r="G7" s="234" t="s">
         <v>608</v>
@@ -65901,19 +66014,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="234">
-        <v>6416</v>
+        <v>6337</v>
       </c>
       <c r="C8" s="235" t="s">
         <v>89</v>
       </c>
       <c r="D8" s="235" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8" s="234" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F8" s="236">
-        <v>15435</v>
+        <v>15680</v>
       </c>
       <c r="G8" s="234" t="s">
         <v>608</v>
@@ -65931,19 +66044,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="234">
-        <v>5782</v>
+        <v>6416</v>
       </c>
       <c r="C9" s="235" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D9" s="235" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E9" s="234" t="s">
         <v>610</v>
       </c>
       <c r="F9" s="236">
-        <v>74464</v>
+        <v>15435</v>
       </c>
       <c r="G9" s="234" t="s">
         <v>608</v>
@@ -65953,7 +66066,7 @@
       </c>
       <c r="I9" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B9)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>1285</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65961,19 +66074,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="234">
-        <v>6531</v>
+        <v>5782</v>
       </c>
       <c r="C10" s="235" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="235" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E10" s="234" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F10" s="236">
-        <v>4320</v>
+        <v>74464</v>
       </c>
       <c r="G10" s="234" t="s">
         <v>608</v>
@@ -65983,7 +66096,7 @@
       </c>
       <c r="I10" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B10)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65991,19 +66104,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="234">
-        <v>6530</v>
+        <v>6531</v>
       </c>
       <c r="C11" s="235" t="s">
         <v>100</v>
       </c>
       <c r="D11" s="235" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" s="234" t="s">
         <v>612</v>
       </c>
       <c r="F11" s="236">
-        <v>4500</v>
+        <v>4320</v>
       </c>
       <c r="G11" s="234" t="s">
         <v>608</v>
@@ -66017,51 +66130,53 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="238">
+      <c r="A12" s="234">
         <v>9</v>
       </c>
-      <c r="B12" s="238">
-        <v>6206</v>
-      </c>
-      <c r="C12" s="239" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="239" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="238" t="s">
-        <v>611</v>
-      </c>
-      <c r="F12" s="240">
-        <v>4704</v>
-      </c>
-      <c r="G12" s="238" t="s">
-        <v>613</v>
-      </c>
-      <c r="H12" s="241" t="s">
-        <v>614</v>
+      <c r="B12" s="234">
+        <v>6530</v>
+      </c>
+      <c r="C12" s="235" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="235" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="234" t="s">
+        <v>612</v>
+      </c>
+      <c r="F12" s="236">
+        <v>4500</v>
+      </c>
+      <c r="G12" s="234" t="s">
+        <v>608</v>
+      </c>
+      <c r="H12" s="237" t="s">
+        <v>609</v>
       </c>
       <c r="I12" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B12)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>68</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="238">
         <v>10</v>
       </c>
-      <c r="B13" s="238"/>
+      <c r="B13" s="238">
+        <v>6206</v>
+      </c>
       <c r="C13" s="239" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D13" s="239" t="s">
-        <v>615</v>
+        <v>35</v>
       </c>
       <c r="E13" s="238" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="F13" s="240">
-        <v>4704</v>
+        <v>8000</v>
       </c>
       <c r="G13" s="238" t="s">
         <v>613</v>
@@ -66071,37 +66186,35 @@
       </c>
       <c r="I13" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B13)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="234">
+      <c r="A14" s="238">
         <v>11</v>
       </c>
-      <c r="B14" s="234">
-        <v>5699</v>
-      </c>
-      <c r="C14" s="235" t="s">
+      <c r="B14" s="238"/>
+      <c r="C14" s="239" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="235" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="234" t="s">
-        <v>617</v>
-      </c>
-      <c r="F14" s="236">
-        <v>14790</v>
-      </c>
-      <c r="G14" s="234" t="s">
-        <v>608</v>
-      </c>
-      <c r="H14" s="237" t="s">
-        <v>618</v>
+      <c r="D14" s="239" t="s">
+        <v>615</v>
+      </c>
+      <c r="E14" s="238" t="s">
+        <v>616</v>
+      </c>
+      <c r="F14" s="240">
+        <v>4704</v>
+      </c>
+      <c r="G14" s="238" t="s">
+        <v>613</v>
+      </c>
+      <c r="H14" s="241" t="s">
+        <v>614</v>
       </c>
       <c r="I14" s="87">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B14)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>6971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66109,19 +66222,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="234">
-        <v>5731</v>
+        <v>5699</v>
       </c>
       <c r="C15" s="235" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="235" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" s="234" t="s">
         <v>617</v>
       </c>
       <c r="F15" s="236">
-        <v>13770</v>
+        <v>14790</v>
       </c>
       <c r="G15" s="234" t="s">
         <v>608</v>
@@ -66135,33 +66248,33 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="238">
+      <c r="A16" s="234">
         <v>13</v>
       </c>
-      <c r="B16" s="238">
-        <v>6624</v>
-      </c>
-      <c r="C16" s="239" t="s">
+      <c r="B16" s="234">
+        <v>5731</v>
+      </c>
+      <c r="C16" s="235" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="239" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="238" t="s">
-        <v>619</v>
-      </c>
-      <c r="F16" s="240">
-        <v>15876</v>
-      </c>
-      <c r="G16" s="238" t="s">
-        <v>613</v>
-      </c>
-      <c r="H16" s="241" t="s">
+      <c r="D16" s="235" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="234" t="s">
+        <v>617</v>
+      </c>
+      <c r="F16" s="236">
+        <v>13770</v>
+      </c>
+      <c r="G16" s="234" t="s">
+        <v>608</v>
+      </c>
+      <c r="H16" s="237" t="s">
         <v>618</v>
       </c>
       <c r="I16" s="87">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B16)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>80</v>
+        <v>6971</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66169,19 +66282,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="238">
-        <v>5731</v>
+        <v>6624</v>
       </c>
       <c r="C17" s="239" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="239" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E17" s="238" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F17" s="240">
-        <v>33660</v>
+        <v>15876</v>
       </c>
       <c r="G17" s="238" t="s">
         <v>613</v>
@@ -66191,7 +66304,7 @@
       </c>
       <c r="I17" s="87">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B17)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>6971</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66199,43 +66312,59 @@
         <v>15</v>
       </c>
       <c r="B18" s="238">
-        <v>6530</v>
+        <v>5731</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D18" s="239" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E18" s="238" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F18" s="240">
-        <v>11340</v>
+        <v>33660</v>
       </c>
       <c r="G18" s="238" t="s">
         <v>613</v>
       </c>
       <c r="H18" s="241" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="I18" s="87">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B18)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>6971</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="242"/>
-      <c r="B19" s="242"/>
-      <c r="C19" s="243"/>
-      <c r="D19" s="243"/>
-      <c r="E19" s="242"/>
-      <c r="F19" s="244"/>
-      <c r="G19" s="242"/>
-      <c r="H19" s="245"/>
+      <c r="A19" s="238">
+        <v>16</v>
+      </c>
+      <c r="B19" s="238">
+        <v>6530</v>
+      </c>
+      <c r="C19" s="239" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="239" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="238" t="s">
+        <v>612</v>
+      </c>
+      <c r="F19" s="240">
+        <v>11340</v>
+      </c>
+      <c r="G19" s="238" t="s">
+        <v>613</v>
+      </c>
+      <c r="H19" s="241" t="s">
+        <v>620</v>
+      </c>
       <c r="I19" s="87">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B19)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>0</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69507,6 +69636,7 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A156:F156"/>
@@ -69515,7 +69645,6 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A22:F22"/>

--- a/Tubex_July26.xlsx
+++ b/Tubex_July26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_61FFE786B3565ECE4A22AAC1A794E696CD1358C5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BAC06EBB44B837774F6352882221B8CA4BEDE9B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4521" uniqueCount="624">
   <si>
     <t>JULY 2026 Tube Required Orders</t>
   </si>
@@ -1859,7 +1859,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 30-Jul-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 01-Aug-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -1904,19 +1904,19 @@
     <t>Not Ready</t>
   </si>
   <si>
-    <t>Inprogess on Packing</t>
+    <t>Inprogress On Packing</t>
   </si>
   <si>
-    <t>Inprogess on Latex</t>
+    <t>Samsol 45</t>
   </si>
   <si>
-    <t>20.5</t>
+    <t>dia 25</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>Order Cancel</t>
-  </si>
-  <si>
-    <t>19</t>
   </si>
   <si>
     <t>Cap Not Available</t>
@@ -3916,8 +3916,8 @@
     <col min="13" max="13" width="14.7109375" style="118" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="118" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="118" customWidth="1"/>
-    <col min="16" max="119" width="8.7109375" style="118" customWidth="1"/>
-    <col min="120" max="16384" width="8.7109375" style="118"/>
+    <col min="16" max="120" width="8.7109375" style="118" customWidth="1"/>
+    <col min="121" max="16384" width="8.7109375" style="118"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4093,18 +4093,18 @@
       <c r="A6" s="115"/>
       <c r="B6" s="251">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>24276</v>
+        <v>26068</v>
       </c>
       <c r="C6" s="248"/>
       <c r="D6" s="124">
         <f>SUMIF($B$11:$B$64,"TUBE",$H$11:$H$64)</f>
-        <v>352100</v>
+        <v>401324</v>
       </c>
       <c r="E6" s="251"/>
       <c r="F6" s="248"/>
       <c r="G6" s="125">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),"-")</f>
-        <v>2.3625977483223339E-2</v>
+        <v>2.3290678374471276E-2</v>
       </c>
       <c r="H6" s="125"/>
       <c r="I6" s="122"/>
@@ -4195,13 +4195,13 @@
       <c r="C8" s="248"/>
       <c r="D8" s="130">
         <f>SUMIF($B$11:$B$64,"PET",$H$11:$H$64)</f>
-        <v>88475</v>
+        <v>94340</v>
       </c>
       <c r="E8" s="256"/>
       <c r="F8" s="248"/>
       <c r="G8" s="131">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),0)</f>
-        <v>7.4771241830065366E-2</v>
+        <v>7.4553659015106924E-2</v>
       </c>
       <c r="H8" s="131"/>
       <c r="I8" s="129"/>
@@ -4443,15 +4443,15 @@
       </c>
       <c r="H12" s="239">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F12)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>39466</v>
+        <v>45850</v>
       </c>
       <c r="I12" s="238">
         <f>G12-H12</f>
-        <v>66064</v>
+        <v>59680</v>
       </c>
       <c r="J12" s="240">
         <f>IF(G12=0,"-",H12/G12)</f>
-        <v>0.3739789633279636</v>
+        <v>0.43447360940017055</v>
       </c>
       <c r="K12" s="239"/>
       <c r="L12" s="241" t="s">
@@ -4589,15 +4589,15 @@
       </c>
       <c r="H14" s="239">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F14)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>189392</v>
+        <v>232232</v>
       </c>
       <c r="I14" s="238">
         <f>G14-H14</f>
-        <v>300000</v>
+        <v>257160</v>
       </c>
       <c r="J14" s="240">
         <f>IF(G14=0,"-",H14/G14)</f>
-        <v>0.38699447477686599</v>
+        <v>0.47453166377872952</v>
       </c>
       <c r="K14" s="239">
         <v>236572</v>
@@ -4703,11 +4703,11 @@
       </c>
       <c r="H16" s="245">
         <f>SUM(H11:H15)</f>
-        <v>352100</v>
+        <v>401324</v>
       </c>
       <c r="I16" s="245">
         <f>SUMIF(I11:I15,"&gt;"&amp;0)</f>
-        <v>401552</v>
+        <v>352328</v>
       </c>
       <c r="J16" s="245"/>
       <c r="K16" s="245">
@@ -4926,15 +4926,15 @@
       </c>
       <c r="H20" s="239">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F20)*Production_Log!$H$3:$H$8963)</f>
-        <v>11155</v>
+        <v>17020</v>
       </c>
       <c r="I20" s="238">
         <f t="shared" si="1"/>
-        <v>230512</v>
+        <v>224647</v>
       </c>
       <c r="J20" s="240">
         <f t="shared" si="2"/>
-        <v>4.6158557022679972E-2</v>
+        <v>7.0427489065532325E-2</v>
       </c>
       <c r="K20" s="239">
         <v>35650</v>
@@ -5131,11 +5131,11 @@
       </c>
       <c r="H24" s="245">
         <f>SUM(H17:H23)</f>
-        <v>88475</v>
+        <v>94340</v>
       </c>
       <c r="I24" s="245">
         <f>SUMIF(I17:I23,"&gt;"&amp;0)</f>
-        <v>283672</v>
+        <v>277807</v>
       </c>
       <c r="J24" s="245"/>
       <c r="K24" s="245">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="G3" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$56,MATCH(MRP!D3,Tubex_Dashboard!$F$11:$F$56,0))</f>
-        <v>39466</v>
+        <v>45850</v>
       </c>
       <c r="H3" s="157">
         <f>F3-G3</f>
-        <v>66064</v>
+        <v>59680</v>
       </c>
       <c r="I3" s="157"/>
     </row>
@@ -9124,11 +9124,11 @@
       </c>
       <c r="G6" s="163">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D6,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>189392</v>
+        <v>232232</v>
       </c>
       <c r="H6" s="164">
         <f>F6-G6</f>
-        <v>300000</v>
+        <v>257160</v>
       </c>
       <c r="I6" s="164"/>
     </row>
@@ -9146,11 +9146,11 @@
       </c>
       <c r="G7" s="135">
         <f>SUM(G3:G6)</f>
-        <v>352100</v>
+        <v>401324</v>
       </c>
       <c r="H7" s="135">
         <f>SUMIF(H3:H6, "&gt;0")</f>
-        <v>401552</v>
+        <v>352328</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="11"/>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="E17" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A17)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>660.97150240000008</v>
+        <v>619.41996159999997</v>
       </c>
       <c r="F17" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A17,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A17,TableInventory[Item ID],0)),0)</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G17" s="31">
         <f t="shared" si="0"/>
-        <v>-227.97150240000008</v>
+        <v>-186.41996159999997</v>
       </c>
       <c r="H17" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A17)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A17)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A17)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A17)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A17)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A17)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A17)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A17)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A17)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A17)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A17)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A17)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="E20" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A20)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>2640</v>
+        <v>2263.0079999999998</v>
       </c>
       <c r="F20" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A20,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A20,TableInventory[Item ID],0)),0)</f>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G20" s="31">
         <f t="shared" si="0"/>
-        <v>-2469</v>
+        <v>-2092.0079999999998</v>
       </c>
       <c r="H20" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="E28" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A28)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>128.20780896000002</v>
+        <v>112.96254816000001</v>
       </c>
       <c r="F28" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A28,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A28,TableInventory[Item ID],0)),0)</f>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="G28" s="31">
         <f t="shared" si="0"/>
-        <v>-28.207808960000023</v>
+        <v>-12.962548160000011</v>
       </c>
       <c r="H28" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A28)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A28)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A28)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A28)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A28)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A28)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A28)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A28)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A28)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A28)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A28)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A28)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="E32" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A32)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>289.3867328</v>
+        <v>253.51594400000002</v>
       </c>
       <c r="F32" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A32,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A32,TableInventory[Item ID],0)),0)</f>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G32" s="31">
         <f t="shared" si="0"/>
-        <v>-139.3867328</v>
+        <v>-103.51594400000002</v>
       </c>
       <c r="H32" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="E40" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A40)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>92.40000000000002</v>
+        <v>79.205280000000016</v>
       </c>
       <c r="F40" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A40,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A40,TableInventory[Item ID],0)),0)</f>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="G40" s="31">
         <f t="shared" si="0"/>
-        <v>-47.40000000000002</v>
+        <v>-34.205280000000016</v>
       </c>
       <c r="H40" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A40)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A40)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A40)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A40)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A40)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A40)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A40)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A40)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A40)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A40)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A40)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A40)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="E55" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A55)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>409583.04000000004</v>
+        <v>359374.56</v>
       </c>
       <c r="F55" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A55,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A55,TableInventory[Item ID],0)),0)</f>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="G55" s="31">
         <f t="shared" si="3"/>
-        <v>-149583.04000000004</v>
+        <v>-99374.56</v>
       </c>
       <c r="H55" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A55)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A55)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A55)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A55)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A55)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A55)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A55)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A55)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A55)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A55)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A55)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A55)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="E68" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A68)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>1718.9686272000001</v>
+        <v>1500.0737664000001</v>
       </c>
       <c r="F68" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A68,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A68,TableInventory[Item ID],0)),0)</f>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="G68" s="31">
         <f t="shared" si="3"/>
-        <v>-1218.9686272000001</v>
+        <v>-1000.0737664000001</v>
       </c>
       <c r="H68" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A68)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A68)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A68)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A68)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A68)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A68)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A68)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A68)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A68)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A68)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A68)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A68)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="E72" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A72)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>3.4325992800000003</v>
+        <v>2.9973398399999995</v>
       </c>
       <c r="F72" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A72,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A72,TableInventory[Item ID],0)),0)</f>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="G72" s="31">
         <f t="shared" si="3"/>
-        <v>16.567400719999998</v>
+        <v>17.002660160000001</v>
       </c>
       <c r="H72" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A72)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A72)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A72)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A72)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A72)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A72)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A72)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A72)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A72)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A72)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A72)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A72)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="E74" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A74)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$6,TableBOM[Product ID],$H$3:$H$6)/1000)</f>
-        <v>241.16236319999999</v>
+        <v>233.25624960000002</v>
       </c>
       <c r="F74" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A74,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A74,TableInventory[Item ID],0)),0)</f>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="G74" s="31">
         <f t="shared" ref="G74:G105" si="6">F74-E74</f>
-        <v>221.83763680000001</v>
+        <v>229.74375039999998</v>
       </c>
       <c r="H74" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ",""))-2),"")</f>
@@ -12474,11 +12474,11 @@
       </c>
       <c r="G101" s="210">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D101,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>11155</v>
+        <v>17020</v>
       </c>
       <c r="H101" s="211">
         <f t="shared" si="7"/>
-        <v>230512</v>
+        <v>224647</v>
       </c>
       <c r="I101" s="212"/>
     </row>
@@ -12496,11 +12496,11 @@
       </c>
       <c r="G102" s="135">
         <f>SUM(G96:G101)</f>
-        <v>88475</v>
+        <v>94340</v>
       </c>
       <c r="H102" s="135">
         <f>SUM(H96:H101)</f>
-        <v>283672</v>
+        <v>277807</v>
       </c>
       <c r="I102" s="12"/>
       <c r="J102" s="11"/>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="E105" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A105)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>6884.9925000000003</v>
+        <v>6736.6080000000002</v>
       </c>
       <c r="F105" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A105,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A105,TableInventory[Item ID],0)),0)</f>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="G105" s="22">
         <f t="shared" ref="G105:G111" si="8">F105-E105</f>
-        <v>-5334.9925000000003</v>
+        <v>-5186.6080000000002</v>
       </c>
       <c r="H105" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A105)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A105)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A105)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A105)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A105)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A105)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A105)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A105)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="E108" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A108)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>316.90727559999999</v>
+        <v>309.57573234999995</v>
       </c>
       <c r="F108" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A108,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A108,TableInventory[Item ID],0)),0)</f>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G108" s="22">
         <f t="shared" si="8"/>
-        <v>-255.90727559999999</v>
+        <v>-248.57573234999995</v>
       </c>
       <c r="H108" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A108)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A108)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A108)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A108)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A108)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A108)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A108)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A108)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A108)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A108)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A108)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A108)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A108)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A108)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A108)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A108)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A108)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A108)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="E109" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A109)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>2833.8146268</v>
+        <v>2775.1622807999997</v>
       </c>
       <c r="F109" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A109,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A109,TableInventory[Item ID],0)),0)</f>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G109" s="22">
         <f t="shared" si="8"/>
-        <v>-2783.8146268</v>
+        <v>-2725.1622807999997</v>
       </c>
       <c r="H109" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A109)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A109)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A109)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A109)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A109)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A109)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A109)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A109)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="E111" s="32">
         <f>SUMPRODUCT((TableBOM[Item ID]=A111)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$96:$D$101,TableBOM[Product ID],$H$96:$H$101)/1000)</f>
-        <v>1.631114</v>
+        <v>1.5973902499999999</v>
       </c>
       <c r="F111" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A111,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A111,TableInventory[Item ID],0)),0)</f>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="G111" s="22">
         <f t="shared" si="8"/>
-        <v>-1.631114</v>
+        <v>-1.5973902499999999</v>
       </c>
       <c r="H111" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A111)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A111)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$96,TableBOM[Item ID],$A111)&gt;0)*($H$96&gt;0),$C$96&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$97,TableBOM[Item ID],$A111)&gt;0)*($H$97&gt;0),$C$97&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A111)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A111)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A111)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A111)&gt;0)*($H$101&gt;0),$C$101&amp;", ",""))-2),"")</f>
@@ -20749,277 +20749,554 @@
       <c r="S148" s="218"/>
     </row>
     <row r="149" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="181"/>
-      <c r="B149" s="182"/>
-      <c r="C149" s="182"/>
-      <c r="D149" s="182"/>
-      <c r="E149" s="182"/>
-      <c r="F149" s="182"/>
-      <c r="G149" s="183"/>
-      <c r="H149" s="183"/>
-      <c r="I149" s="183"/>
-      <c r="J149" s="184"/>
-      <c r="K149" s="182"/>
-      <c r="L149" s="182"/>
-      <c r="M149" s="182"/>
-      <c r="N149" s="182"/>
-      <c r="O149" s="182"/>
-      <c r="P149" s="182"/>
-      <c r="Q149" s="182"/>
-      <c r="R149" s="182"/>
-      <c r="S149" s="182"/>
+      <c r="A149" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B149" s="218" t="s">
+        <v>296</v>
+      </c>
+      <c r="C149" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D149" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="218">
+        <v>30</v>
+      </c>
+      <c r="F149" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G149" s="219">
+        <v>26000</v>
+      </c>
+      <c r="H149" s="219">
+        <v>25590</v>
+      </c>
+      <c r="I149" s="219">
+        <v>410</v>
+      </c>
+      <c r="J149" s="220">
+        <f t="shared" si="4"/>
+        <v>1.5769230769230768E-2</v>
+      </c>
+      <c r="K149" s="218"/>
+      <c r="L149" s="218"/>
+      <c r="M149" s="218"/>
+      <c r="N149" s="218"/>
+      <c r="O149" s="218"/>
+      <c r="P149" s="218"/>
+      <c r="Q149" s="218"/>
+      <c r="R149" s="218"/>
+      <c r="S149" s="218"/>
     </row>
     <row r="150" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="181"/>
-      <c r="B150" s="182"/>
-      <c r="C150" s="182"/>
-      <c r="D150" s="182"/>
-      <c r="E150" s="182"/>
-      <c r="F150" s="182"/>
-      <c r="G150" s="183"/>
-      <c r="H150" s="183"/>
-      <c r="I150" s="183"/>
-      <c r="J150" s="184"/>
-      <c r="K150" s="182"/>
-      <c r="L150" s="182"/>
-      <c r="M150" s="182"/>
-      <c r="N150" s="182"/>
-      <c r="O150" s="182"/>
-      <c r="P150" s="182"/>
-      <c r="Q150" s="182"/>
-      <c r="R150" s="182"/>
-      <c r="S150" s="182"/>
+      <c r="A150" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B150" s="218" t="s">
+        <v>297</v>
+      </c>
+      <c r="C150" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D150" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="218">
+        <v>30</v>
+      </c>
+      <c r="F150" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G150" s="219">
+        <v>11424</v>
+      </c>
+      <c r="H150" s="219">
+        <v>11414</v>
+      </c>
+      <c r="I150" s="219">
+        <v>10</v>
+      </c>
+      <c r="J150" s="220">
+        <f t="shared" si="4"/>
+        <v>8.7535014005602244E-4</v>
+      </c>
+      <c r="K150" s="218"/>
+      <c r="L150" s="218"/>
+      <c r="M150" s="218"/>
+      <c r="N150" s="218"/>
+      <c r="O150" s="218"/>
+      <c r="P150" s="218"/>
+      <c r="Q150" s="218"/>
+      <c r="R150" s="218"/>
+      <c r="S150" s="218"/>
     </row>
     <row r="151" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="181"/>
-      <c r="B151" s="182"/>
-      <c r="C151" s="182"/>
-      <c r="D151" s="182"/>
-      <c r="E151" s="182"/>
-      <c r="F151" s="182"/>
-      <c r="G151" s="183"/>
-      <c r="H151" s="183"/>
-      <c r="I151" s="183"/>
-      <c r="J151" s="184"/>
-      <c r="K151" s="182"/>
-      <c r="L151" s="182"/>
-      <c r="M151" s="182"/>
-      <c r="N151" s="182"/>
-      <c r="O151" s="182"/>
-      <c r="P151" s="182"/>
-      <c r="Q151" s="182"/>
-      <c r="R151" s="182"/>
-      <c r="S151" s="182"/>
+      <c r="A151" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B151" s="218" t="s">
+        <v>297</v>
+      </c>
+      <c r="C151" s="218" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151" s="218" t="s">
+        <v>15</v>
+      </c>
+      <c r="E151" s="218">
+        <v>30</v>
+      </c>
+      <c r="F151" s="218">
+        <v>5814</v>
+      </c>
+      <c r="G151" s="219">
+        <v>12600</v>
+      </c>
+      <c r="H151" s="219">
+        <v>12590</v>
+      </c>
+      <c r="I151" s="219">
+        <v>10</v>
+      </c>
+      <c r="J151" s="220">
+        <f t="shared" si="4"/>
+        <v>7.9365079365079365E-4</v>
+      </c>
+      <c r="K151" s="218"/>
+      <c r="L151" s="218"/>
+      <c r="M151" s="218"/>
+      <c r="N151" s="218"/>
+      <c r="O151" s="218"/>
+      <c r="P151" s="218"/>
+      <c r="Q151" s="218"/>
+      <c r="R151" s="218"/>
+      <c r="S151" s="218"/>
     </row>
     <row r="152" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="181"/>
-      <c r="B152" s="182"/>
-      <c r="C152" s="182"/>
-      <c r="D152" s="182"/>
-      <c r="E152" s="182"/>
-      <c r="F152" s="182"/>
-      <c r="G152" s="183"/>
-      <c r="H152" s="183"/>
-      <c r="I152" s="183"/>
-      <c r="J152" s="184"/>
-      <c r="K152" s="182"/>
-      <c r="L152" s="182"/>
-      <c r="M152" s="182"/>
-      <c r="N152" s="182"/>
-      <c r="O152" s="182"/>
-      <c r="P152" s="182"/>
-      <c r="Q152" s="182"/>
-      <c r="R152" s="182"/>
-      <c r="S152" s="182"/>
+      <c r="A152" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B152" s="218" t="s">
+        <v>298</v>
+      </c>
+      <c r="C152" s="218" t="s">
+        <v>143</v>
+      </c>
+      <c r="D152" s="218" t="s">
+        <v>221</v>
+      </c>
+      <c r="E152" s="218" t="s">
+        <v>142</v>
+      </c>
+      <c r="F152" s="218">
+        <v>8001</v>
+      </c>
+      <c r="G152" s="219">
+        <v>0</v>
+      </c>
+      <c r="H152" s="219">
+        <v>0</v>
+      </c>
+      <c r="I152" s="219">
+        <v>0</v>
+      </c>
+      <c r="J152" s="220" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K152" s="218">
+        <v>960</v>
+      </c>
+      <c r="L152" s="218"/>
+      <c r="M152" s="218"/>
+      <c r="N152" s="218"/>
+      <c r="O152" s="218"/>
+      <c r="P152" s="218"/>
+      <c r="Q152" s="218"/>
+      <c r="R152" s="218"/>
+      <c r="S152" s="218"/>
     </row>
     <row r="153" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="181"/>
-      <c r="B153" s="182"/>
-      <c r="C153" s="182"/>
-      <c r="D153" s="182"/>
-      <c r="E153" s="182"/>
-      <c r="F153" s="182"/>
-      <c r="G153" s="183"/>
-      <c r="H153" s="183"/>
-      <c r="I153" s="183"/>
-      <c r="J153" s="184"/>
-      <c r="K153" s="182"/>
-      <c r="L153" s="182"/>
-      <c r="M153" s="182"/>
-      <c r="N153" s="182"/>
-      <c r="O153" s="182"/>
-      <c r="P153" s="182"/>
-      <c r="Q153" s="182"/>
-      <c r="R153" s="182"/>
-      <c r="S153" s="182"/>
+      <c r="A153" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B153" s="218" t="s">
+        <v>299</v>
+      </c>
+      <c r="C153" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D153" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="218">
+        <v>30</v>
+      </c>
+      <c r="F153" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G153" s="219">
+        <v>22000</v>
+      </c>
+      <c r="H153" s="219">
+        <v>21850</v>
+      </c>
+      <c r="I153" s="219">
+        <v>150</v>
+      </c>
+      <c r="J153" s="220">
+        <f t="shared" si="4"/>
+        <v>6.8181818181818179E-3</v>
+      </c>
+      <c r="K153" s="218"/>
+      <c r="L153" s="218"/>
+      <c r="M153" s="218"/>
+      <c r="N153" s="218"/>
+      <c r="O153" s="218"/>
+      <c r="P153" s="218"/>
+      <c r="Q153" s="218"/>
+      <c r="R153" s="218"/>
+      <c r="S153" s="218"/>
     </row>
     <row r="154" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="181"/>
-      <c r="B154" s="182"/>
-      <c r="C154" s="182"/>
-      <c r="D154" s="182"/>
-      <c r="E154" s="182"/>
-      <c r="F154" s="182"/>
-      <c r="G154" s="183"/>
-      <c r="H154" s="183"/>
-      <c r="I154" s="183"/>
-      <c r="J154" s="184"/>
-      <c r="K154" s="182"/>
-      <c r="L154" s="182"/>
-      <c r="M154" s="182"/>
-      <c r="N154" s="182"/>
-      <c r="O154" s="182"/>
-      <c r="P154" s="182"/>
-      <c r="Q154" s="182"/>
-      <c r="R154" s="182"/>
-      <c r="S154" s="182"/>
+      <c r="A154" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B154" s="218" t="s">
+        <v>301</v>
+      </c>
+      <c r="C154" s="218" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="218" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" s="218">
+        <v>25</v>
+      </c>
+      <c r="F154" s="218">
+        <v>5389</v>
+      </c>
+      <c r="G154" s="219">
+        <v>2808</v>
+      </c>
+      <c r="H154" s="219">
+        <v>2688</v>
+      </c>
+      <c r="I154" s="219">
+        <v>120</v>
+      </c>
+      <c r="J154" s="220">
+        <f t="shared" si="4"/>
+        <v>4.2735042735042736E-2</v>
+      </c>
+      <c r="K154" s="218"/>
+      <c r="L154" s="218"/>
+      <c r="M154" s="218"/>
+      <c r="N154" s="218"/>
+      <c r="O154" s="218"/>
+      <c r="P154" s="218"/>
+      <c r="Q154" s="218"/>
+      <c r="R154" s="218"/>
+      <c r="S154" s="218"/>
     </row>
     <row r="155" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="181"/>
-      <c r="B155" s="182"/>
-      <c r="C155" s="182"/>
-      <c r="D155" s="182"/>
-      <c r="E155" s="182"/>
-      <c r="F155" s="182"/>
-      <c r="G155" s="183"/>
-      <c r="H155" s="183"/>
-      <c r="I155" s="183"/>
-      <c r="J155" s="184"/>
-      <c r="K155" s="182"/>
-      <c r="L155" s="182"/>
-      <c r="M155" s="182"/>
-      <c r="N155" s="182"/>
-      <c r="O155" s="182"/>
-      <c r="P155" s="182"/>
-      <c r="Q155" s="182"/>
-      <c r="R155" s="182"/>
-      <c r="S155" s="182"/>
+      <c r="A155" s="217">
+        <v>46233</v>
+      </c>
+      <c r="B155" s="218" t="s">
+        <v>304</v>
+      </c>
+      <c r="C155" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D155" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="218">
+        <v>30</v>
+      </c>
+      <c r="F155" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G155" s="219">
+        <v>20863</v>
+      </c>
+      <c r="H155" s="219">
+        <v>20468</v>
+      </c>
+      <c r="I155" s="219">
+        <v>395</v>
+      </c>
+      <c r="J155" s="220">
+        <f t="shared" si="4"/>
+        <v>1.8933039351962805E-2</v>
+      </c>
+      <c r="K155" s="218"/>
+      <c r="L155" s="218"/>
+      <c r="M155" s="218"/>
+      <c r="N155" s="218"/>
+      <c r="O155" s="218"/>
+      <c r="P155" s="218"/>
+      <c r="Q155" s="218"/>
+      <c r="R155" s="218"/>
+      <c r="S155" s="218"/>
     </row>
     <row r="156" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="181"/>
-      <c r="B156" s="182"/>
-      <c r="C156" s="182"/>
-      <c r="D156" s="182"/>
-      <c r="E156" s="182"/>
-      <c r="F156" s="182"/>
-      <c r="G156" s="183"/>
-      <c r="H156" s="183"/>
-      <c r="I156" s="183"/>
-      <c r="J156" s="184"/>
-      <c r="K156" s="182"/>
-      <c r="L156" s="182"/>
-      <c r="M156" s="182"/>
-      <c r="N156" s="182"/>
-      <c r="O156" s="182"/>
-      <c r="P156" s="182"/>
-      <c r="Q156" s="182"/>
-      <c r="R156" s="182"/>
-      <c r="S156" s="182"/>
+      <c r="A156" s="217">
+        <v>46234</v>
+      </c>
+      <c r="B156" s="218" t="s">
+        <v>296</v>
+      </c>
+      <c r="C156" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D156" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156" s="218">
+        <v>30</v>
+      </c>
+      <c r="F156" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G156" s="219">
+        <v>23000</v>
+      </c>
+      <c r="H156" s="219">
+        <v>22880</v>
+      </c>
+      <c r="I156" s="219">
+        <v>120</v>
+      </c>
+      <c r="J156" s="220">
+        <f t="shared" si="4"/>
+        <v>5.2173913043478265E-3</v>
+      </c>
+      <c r="K156" s="218"/>
+      <c r="L156" s="218"/>
+      <c r="M156" s="218"/>
+      <c r="N156" s="218"/>
+      <c r="O156" s="218"/>
+      <c r="P156" s="218"/>
+      <c r="Q156" s="218"/>
+      <c r="R156" s="218"/>
+      <c r="S156" s="218"/>
     </row>
     <row r="157" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="181"/>
-      <c r="B157" s="182"/>
-      <c r="C157" s="182"/>
-      <c r="D157" s="182"/>
-      <c r="E157" s="182"/>
-      <c r="F157" s="182"/>
-      <c r="G157" s="183"/>
-      <c r="H157" s="183"/>
-      <c r="I157" s="183"/>
-      <c r="J157" s="184"/>
-      <c r="K157" s="182"/>
-      <c r="L157" s="182"/>
-      <c r="M157" s="182"/>
-      <c r="N157" s="182"/>
-      <c r="O157" s="182"/>
-      <c r="P157" s="182"/>
-      <c r="Q157" s="182"/>
-      <c r="R157" s="182"/>
-      <c r="S157" s="182"/>
+      <c r="A157" s="217">
+        <v>46234</v>
+      </c>
+      <c r="B157" s="218" t="s">
+        <v>297</v>
+      </c>
+      <c r="C157" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D157" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="218">
+        <v>30</v>
+      </c>
+      <c r="F157" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G157" s="219">
+        <v>24000</v>
+      </c>
+      <c r="H157" s="219">
+        <v>23980</v>
+      </c>
+      <c r="I157" s="219">
+        <v>20</v>
+      </c>
+      <c r="J157" s="220">
+        <f t="shared" si="4"/>
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="K157" s="218"/>
+      <c r="L157" s="218"/>
+      <c r="M157" s="218"/>
+      <c r="N157" s="218"/>
+      <c r="O157" s="218"/>
+      <c r="P157" s="218"/>
+      <c r="Q157" s="218"/>
+      <c r="R157" s="218"/>
+      <c r="S157" s="218"/>
     </row>
     <row r="158" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="181"/>
-      <c r="B158" s="182"/>
-      <c r="C158" s="182"/>
-      <c r="D158" s="182"/>
-      <c r="E158" s="182"/>
-      <c r="F158" s="182"/>
-      <c r="G158" s="183"/>
-      <c r="H158" s="183"/>
-      <c r="I158" s="183"/>
-      <c r="J158" s="184"/>
-      <c r="K158" s="182"/>
-      <c r="L158" s="182"/>
-      <c r="M158" s="182"/>
-      <c r="N158" s="182"/>
-      <c r="O158" s="182"/>
-      <c r="P158" s="182"/>
-      <c r="Q158" s="182"/>
-      <c r="R158" s="182"/>
-      <c r="S158" s="182"/>
+      <c r="A158" s="217">
+        <v>46234</v>
+      </c>
+      <c r="B158" s="218" t="s">
+        <v>298</v>
+      </c>
+      <c r="C158" s="218" t="s">
+        <v>143</v>
+      </c>
+      <c r="D158" s="218" t="s">
+        <v>221</v>
+      </c>
+      <c r="E158" s="218" t="s">
+        <v>142</v>
+      </c>
+      <c r="F158" s="218">
+        <v>8001</v>
+      </c>
+      <c r="G158" s="219">
+        <v>6315</v>
+      </c>
+      <c r="H158" s="219">
+        <v>5865</v>
+      </c>
+      <c r="I158" s="219">
+        <v>450</v>
+      </c>
+      <c r="J158" s="220">
+        <f t="shared" si="4"/>
+        <v>7.1258907363420429E-2</v>
+      </c>
+      <c r="K158" s="218">
+        <v>120</v>
+      </c>
+      <c r="L158" s="218"/>
+      <c r="M158" s="218"/>
+      <c r="N158" s="218"/>
+      <c r="O158" s="218"/>
+      <c r="P158" s="218"/>
+      <c r="Q158" s="218"/>
+      <c r="R158" s="218"/>
+      <c r="S158" s="218"/>
     </row>
     <row r="159" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="181"/>
-      <c r="B159" s="182"/>
-      <c r="C159" s="182"/>
-      <c r="D159" s="182"/>
-      <c r="E159" s="182"/>
-      <c r="F159" s="182"/>
-      <c r="G159" s="183"/>
-      <c r="H159" s="183"/>
-      <c r="I159" s="183"/>
-      <c r="J159" s="184"/>
-      <c r="K159" s="182"/>
-      <c r="L159" s="182"/>
-      <c r="M159" s="182"/>
-      <c r="N159" s="182"/>
-      <c r="O159" s="182"/>
-      <c r="P159" s="182"/>
-      <c r="Q159" s="182"/>
-      <c r="R159" s="182"/>
-      <c r="S159" s="182"/>
+      <c r="A159" s="217">
+        <v>46234</v>
+      </c>
+      <c r="B159" s="218" t="s">
+        <v>299</v>
+      </c>
+      <c r="C159" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D159" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159" s="218">
+        <v>30</v>
+      </c>
+      <c r="F159" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G159" s="219">
+        <v>25000</v>
+      </c>
+      <c r="H159" s="219">
+        <v>24850</v>
+      </c>
+      <c r="I159" s="219">
+        <v>150</v>
+      </c>
+      <c r="J159" s="220">
+        <f t="shared" si="4"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K159" s="218"/>
+      <c r="L159" s="218"/>
+      <c r="M159" s="218"/>
+      <c r="N159" s="218"/>
+      <c r="O159" s="218"/>
+      <c r="P159" s="218"/>
+      <c r="Q159" s="218"/>
+      <c r="R159" s="218"/>
+      <c r="S159" s="218"/>
     </row>
     <row r="160" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="181"/>
-      <c r="B160" s="182"/>
-      <c r="C160" s="182"/>
-      <c r="D160" s="182"/>
-      <c r="E160" s="182"/>
-      <c r="F160" s="182"/>
-      <c r="G160" s="183"/>
-      <c r="H160" s="183"/>
-      <c r="I160" s="183"/>
-      <c r="J160" s="184"/>
-      <c r="K160" s="182"/>
-      <c r="L160" s="182"/>
-      <c r="M160" s="182"/>
-      <c r="N160" s="182"/>
-      <c r="O160" s="182"/>
-      <c r="P160" s="182"/>
-      <c r="Q160" s="182"/>
-      <c r="R160" s="182"/>
-      <c r="S160" s="182"/>
+      <c r="A160" s="217">
+        <v>46234</v>
+      </c>
+      <c r="B160" s="218" t="s">
+        <v>301</v>
+      </c>
+      <c r="C160" s="218" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="218" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="218">
+        <v>25</v>
+      </c>
+      <c r="F160" s="218">
+        <v>5389</v>
+      </c>
+      <c r="G160" s="219">
+        <v>3846</v>
+      </c>
+      <c r="H160" s="219">
+        <v>3696</v>
+      </c>
+      <c r="I160" s="219">
+        <v>150</v>
+      </c>
+      <c r="J160" s="220">
+        <f t="shared" si="4"/>
+        <v>3.9001560062402497E-2</v>
+      </c>
+      <c r="K160" s="218"/>
+      <c r="L160" s="218"/>
+      <c r="M160" s="218"/>
+      <c r="N160" s="218"/>
+      <c r="O160" s="218"/>
+      <c r="P160" s="218"/>
+      <c r="Q160" s="218"/>
+      <c r="R160" s="218"/>
+      <c r="S160" s="218"/>
     </row>
     <row r="161" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="181"/>
-      <c r="B161" s="182"/>
-      <c r="C161" s="182"/>
-      <c r="D161" s="182"/>
-      <c r="E161" s="182"/>
-      <c r="F161" s="182"/>
-      <c r="G161" s="183"/>
-      <c r="H161" s="183"/>
-      <c r="I161" s="183"/>
-      <c r="J161" s="184"/>
-      <c r="K161" s="182"/>
-      <c r="L161" s="182"/>
-      <c r="M161" s="182"/>
-      <c r="N161" s="182"/>
-      <c r="O161" s="182"/>
-      <c r="P161" s="182"/>
-      <c r="Q161" s="182"/>
-      <c r="R161" s="182"/>
-      <c r="S161" s="182"/>
+      <c r="A161" s="217">
+        <v>46234</v>
+      </c>
+      <c r="B161" s="218" t="s">
+        <v>304</v>
+      </c>
+      <c r="C161" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161" s="218" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161" s="218">
+        <v>30</v>
+      </c>
+      <c r="F161" s="218">
+        <v>6206</v>
+      </c>
+      <c r="G161" s="219">
+        <v>22757</v>
+      </c>
+      <c r="H161" s="219">
+        <v>22372</v>
+      </c>
+      <c r="I161" s="219">
+        <v>385</v>
+      </c>
+      <c r="J161" s="220">
+        <f t="shared" si="4"/>
+        <v>1.6917871424177177E-2</v>
+      </c>
+      <c r="K161" s="218"/>
+      <c r="L161" s="218"/>
+      <c r="M161" s="218"/>
+      <c r="N161" s="218"/>
+      <c r="O161" s="218"/>
+      <c r="P161" s="218"/>
+      <c r="Q161" s="218"/>
+      <c r="R161" s="218"/>
+      <c r="S161" s="218"/>
     </row>
     <row r="162" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="181"/>
@@ -65481,14 +65758,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -65580,7 +65857,7 @@
         <v>611</v>
       </c>
       <c r="F4" s="223">
-        <v>5865</v>
+        <v>6325</v>
       </c>
       <c r="G4" s="221" t="s">
         <v>612</v>
@@ -65598,19 +65875,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="221">
-        <v>5814</v>
+        <v>6206</v>
       </c>
       <c r="C5" s="222" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="222" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="221" t="s">
         <v>614</v>
       </c>
       <c r="F5" s="223">
-        <v>24000</v>
+        <v>22134</v>
       </c>
       <c r="G5" s="221" t="s">
         <v>612</v>
@@ -65620,7 +65897,7 @@
       </c>
       <c r="I5" s="85">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B5)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65838,19 +66115,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="225">
-        <v>5814</v>
+        <v>6206</v>
       </c>
       <c r="C13" s="226" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" s="226" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" s="225" t="s">
         <v>614</v>
       </c>
       <c r="F13" s="227">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="G13" s="225" t="s">
         <v>617</v>
@@ -65860,187 +66137,137 @@
       </c>
       <c r="I13" s="85">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B13)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="225">
         <v>11</v>
       </c>
-      <c r="B14" s="225">
-        <v>5814</v>
-      </c>
+      <c r="B14" s="225"/>
       <c r="C14" s="226" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D14" s="226" t="s">
-        <v>15</v>
+        <v>619</v>
       </c>
       <c r="E14" s="225" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="F14" s="227">
-        <v>5000</v>
+        <v>6384</v>
       </c>
       <c r="G14" s="225" t="s">
         <v>617</v>
       </c>
       <c r="H14" s="228" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I14" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B14)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="221">
+      <c r="A15" s="225">
         <v>12</v>
       </c>
-      <c r="B15" s="221">
-        <v>5699</v>
-      </c>
-      <c r="C15" s="222" t="s">
+      <c r="B15" s="225">
+        <v>6624</v>
+      </c>
+      <c r="C15" s="226" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="222" t="s">
-        <v>235</v>
-      </c>
-      <c r="E15" s="221" t="s">
-        <v>620</v>
-      </c>
-      <c r="F15" s="223">
-        <v>14790</v>
-      </c>
-      <c r="G15" s="221" t="s">
-        <v>612</v>
-      </c>
-      <c r="H15" s="224" t="s">
+      <c r="D15" s="226" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="225" t="s">
         <v>621</v>
+      </c>
+      <c r="F15" s="227">
+        <v>15876</v>
+      </c>
+      <c r="G15" s="225" t="s">
+        <v>617</v>
+      </c>
+      <c r="H15" s="228" t="s">
+        <v>622</v>
       </c>
       <c r="I15" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B15)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>6971</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="221">
+      <c r="A16" s="225">
         <v>13</v>
       </c>
-      <c r="B16" s="221">
-        <v>5731</v>
-      </c>
-      <c r="C16" s="222" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="222" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" s="221" t="s">
-        <v>620</v>
-      </c>
-      <c r="F16" s="223">
-        <v>13770</v>
-      </c>
-      <c r="G16" s="221" t="s">
-        <v>612</v>
-      </c>
-      <c r="H16" s="224" t="s">
-        <v>621</v>
+      <c r="B16" s="225">
+        <v>6530</v>
+      </c>
+      <c r="C16" s="226" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="226" t="s">
+        <v>268</v>
+      </c>
+      <c r="E16" s="225" t="s">
+        <v>616</v>
+      </c>
+      <c r="F16" s="227">
+        <v>11340</v>
+      </c>
+      <c r="G16" s="225" t="s">
+        <v>617</v>
+      </c>
+      <c r="H16" s="228" t="s">
+        <v>623</v>
       </c>
       <c r="I16" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B16)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>6971</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="225">
-        <v>14</v>
-      </c>
-      <c r="B17" s="225">
-        <v>6624</v>
-      </c>
-      <c r="C17" s="226" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="226" t="s">
-        <v>229</v>
-      </c>
-      <c r="E17" s="225" t="s">
-        <v>622</v>
-      </c>
-      <c r="F17" s="227">
-        <v>15876</v>
-      </c>
-      <c r="G17" s="225" t="s">
-        <v>617</v>
-      </c>
-      <c r="H17" s="228" t="s">
-        <v>621</v>
-      </c>
+      <c r="A17" s="229"/>
+      <c r="B17" s="229"/>
+      <c r="C17" s="230"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="231"/>
+      <c r="G17" s="229"/>
+      <c r="H17" s="232"/>
       <c r="I17" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B17)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="225">
-        <v>15</v>
-      </c>
-      <c r="B18" s="225">
-        <v>5731</v>
-      </c>
-      <c r="C18" s="226" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="226" t="s">
-        <v>237</v>
-      </c>
-      <c r="E18" s="225" t="s">
-        <v>620</v>
-      </c>
-      <c r="F18" s="227">
-        <v>33660</v>
-      </c>
-      <c r="G18" s="225" t="s">
-        <v>617</v>
-      </c>
-      <c r="H18" s="228" t="s">
-        <v>621</v>
-      </c>
+      <c r="A18" s="229"/>
+      <c r="B18" s="229"/>
+      <c r="C18" s="230"/>
+      <c r="D18" s="230"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="231"/>
+      <c r="G18" s="229"/>
+      <c r="H18" s="232"/>
       <c r="I18" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B18)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>6971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="225">
-        <v>16</v>
-      </c>
-      <c r="B19" s="225">
-        <v>6530</v>
-      </c>
-      <c r="C19" s="226" t="s">
-        <v>267</v>
-      </c>
-      <c r="D19" s="226" t="s">
-        <v>268</v>
-      </c>
-      <c r="E19" s="225" t="s">
-        <v>616</v>
-      </c>
-      <c r="F19" s="227">
-        <v>11340</v>
-      </c>
-      <c r="G19" s="225" t="s">
-        <v>617</v>
-      </c>
-      <c r="H19" s="228" t="s">
-        <v>623</v>
-      </c>
+      <c r="A19" s="229"/>
+      <c r="B19" s="229"/>
+      <c r="C19" s="230"/>
+      <c r="D19" s="230"/>
+      <c r="E19" s="229"/>
+      <c r="F19" s="231"/>
+      <c r="G19" s="229"/>
+      <c r="H19" s="232"/>
       <c r="I19" s="86">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B19)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
